--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>26642.7</v>
+        <v>27397.66</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7531.87</v>
+        <v>7557.43</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28102.38</v>
+        <v>28553.99</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14057.76</v>
+        <v>14283.67</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>73550.39999999999</v>
+        <v>73712.03</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>23248.49</v>
+        <v>23299.58</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26257.49</v>
+        <v>25923.74</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>218707.38</v>
+        <v>215927.46</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20637.02</v>
+        <v>20374.71</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7935.43</v>
+        <v>7834.57</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>187725.15</v>
+        <v>185339.03</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25634.42</v>
+        <v>25308.59</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35524.85</v>
+        <v>35279.98</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>124323.82</v>
+        <v>123466.9</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>87647.56</v>
+        <v>87043.44</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>57495.4</v>
+        <v>57099.1</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>66458.03999999999</v>
+        <v>65999.97</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>40549.48</v>
+        <v>41291.5</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>46458.46</v>
+        <v>47308.62</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>61966.29</v>
+        <v>62947.37</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13723.74</v>
+        <v>13941.02</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>32345.68</v>
+        <v>32857.8</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>30621.24</v>
+        <v>31106.05</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7491.63</v>
+        <v>7492.49</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>55715.33</v>
+        <v>55721.69</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>72784.25</v>
+        <v>72859.02</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>10993.16</v>
+        <v>11004.45</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>15706.87</v>
+        <v>15723.01</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15316.87</v>
+        <v>15382.69</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>18729.09</v>
+        <v>18809.57</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>58840.32</v>
+        <v>58687.73</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>56017.28</v>
+        <v>55872.01</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1722655.54</v>
+        <v>1703050.45</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>69258.95</v>
+        <v>68470.73</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8876.92</v>
+        <v>8745.969999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4793.03</v>
+        <v>4766.29</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>30278.25</v>
+        <v>30109.31</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>73466.35000000001</v>
+        <v>73056.42999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>50434.56</v>
+        <v>50153.16</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8271.790000000001</v>
+        <v>8225.639999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>32386.41</v>
+        <v>32184.26</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>43875.18</v>
+        <v>43601.31</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>19907.64</v>
+        <v>19825.16</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>20171.64</v>
+        <v>20088.06</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>63155.28</v>
+        <v>61806.72</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>33223.77</v>
+        <v>32456.05</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8816.110000000001</v>
+        <v>8612.389999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>45615.72</v>
+        <v>44561.65</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>33148.03</v>
+        <v>32382.06</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENVISION INVERSIONES LIMITADA </t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -880,7 +884,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1460278-82-CM26</t>
+          <t>1035206-191-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,43 +909,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.827.350-7</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>25923.74</v>
+        <v>185339.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1351461-11-CM26</t>
+          <t>2686-60-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +969,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>69.071.500-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>I MUNICIPALIDAD DE COLINA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +989,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>UBIQUITY SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.423.027-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +1004,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>215927.46</v>
+        <v>7834.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1460278-83-CM26</t>
+          <t>1588-29-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1030,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1050,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+          <t>Smartnodus SpA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.827.350-7</t>
+          <t>76.461.797-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1065,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20374.71</v>
+        <v>25308.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2686-60-CM26</t>
+          <t>1351461-11-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,17 +1091,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.071.500-7</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLINA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1111,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>UBIQUITY SPA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.423.027-2</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1126,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7834.57</v>
+        <v>215927.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1035206-191-CM25</t>
+          <t>1460278-82-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,43 +1157,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>96.827.350-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>185339.03</v>
+        <v>25923.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1588-29-CM26</t>
+          <t>1460278-83-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,17 +1217,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,28 +1237,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Smartnodus SpA</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.461.797-5</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>96.827.350-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25308.59</v>
+        <v>20374.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>45-46-CM26</t>
+          <t>4956-49-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,17 +1282,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1302,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENVISION INVERSIONES LIMITADA</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1317,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35279.98</v>
+        <v>65999.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>874750-67-CM26</t>
+          <t>3553-82-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,48 +1343,52 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>SERVICIOS Y COMERCIALIZACIÓN CAIFU SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>77.843.971-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>123466.9</v>
+        <v>57099.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1233623-50-CM26</t>
+          <t>45-46-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,27 +1413,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Andestic SpA</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1443,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>87043.44</v>
+        <v>35279.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3553-82-CM26</t>
+          <t>874750-67-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,32 +1469,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SERVICIOS Y COMERCIALIZACIÓN CAIFU SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.843.971-9</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1504,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>57099.1</v>
+        <v>123466.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4956-49-CM26</t>
+          <t>1233623-50-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,32 +1530,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,7 +1565,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>65999.97</v>
+        <v>87043.44</v>
       </c>
     </row>
     <row r="19">
@@ -1673,7 +1693,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>548874-73-CM26</t>
+          <t>2663-119-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,43 +1718,47 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.681.168-8</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>62947.37</v>
+        <v>13941.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2663-119-CM26</t>
+          <t>2686-128-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,32 +1778,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.071.500-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>I MUNICIPALIDAD DE COLINA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1813,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13941.02</v>
+        <v>32857.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2686-128-CM26</t>
+          <t>548874-73-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1839,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.071.500-7</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLINA</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,22 +1859,26 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.681.168-8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>32857.8</v>
+        <v>62947.37</v>
       </c>
     </row>
     <row r="24">
@@ -2026,7 +2054,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2039,7 +2071,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1093219-4-CM26</t>
+          <t>5416-143-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,27 +2096,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2126,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>72859.02</v>
+        <v>15723.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>568963-69-CM26</t>
+          <t>1093219-4-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2157,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.979.610-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,28 +2172,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>96.986.170-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11004.45</v>
+        <v>72859.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5416-143-CM26</t>
+          <t>568963-69-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,27 +2222,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.979.610-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2252,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>15723.01</v>
+        <v>11004.45</v>
       </c>
     </row>
     <row r="30">
@@ -2392,7 +2428,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2554,11 @@
           <t>77.866.212-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2619,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2649,7 +2697,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2434-30-SE26</t>
+          <t>2799-334-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,52 +2717,48 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4766.29</v>
+        <v>30109.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2799-334-CM26</t>
+          <t>2434-30-SE26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2734,42 +2778,46 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>30109.31</v>
+        <v>4766.29</v>
       </c>
     </row>
     <row r="39">
@@ -2823,7 +2871,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +2936,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3062,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3019,7 +3079,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1469-528-CM26</t>
+          <t>1499-1741-SE26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3039,48 +3099,52 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.608.402-k</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.227.643-7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>43601.31</v>
+        <v>93011.27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1973-722-CM26</t>
+          <t>1469-528-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,53 +3159,57 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.953.200-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>19825.16</v>
+        <v>43601.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>872535-79-CM26</t>
+          <t>1973-722-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3166,27 +3234,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.953.200-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,13 +3264,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>20088.06</v>
+        <v>19825.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1393093-359-CM26</t>
+          <t>872535-79-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3217,7 +3285,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,27 +3295,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Andestic SpA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,13 +3325,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>61806.72</v>
+        <v>20088.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2446-288-CM26</t>
+          <t>1393093-359-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3278,7 +3346,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3288,27 +3356,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,7 +3386,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>32456.05</v>
+        <v>61806.72</v>
       </c>
     </row>
     <row r="48">
@@ -3385,7 +3453,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1191449-8-CM26</t>
+          <t>1057547-4819-SE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3410,43 +3478,47 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>BRAINSOFT</t>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.261.280-1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>44561.65</v>
+        <v>47438.21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2423-543-CM26</t>
+          <t>1191449-8-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3466,17 +3538,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.072.100-7</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3558,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>BRAINSOFT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.261.280-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,6 +3573,128 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
+        <v>44561.65</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2446-288-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MEETCARD</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.437.288-3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>32456.05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2423-543-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.072.100-7</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SolNet SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
         <v>32382.06</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
@@ -1680,7 +1680,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
